--- a/work_plans.xlsx
+++ b/work_plans.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3018FF-2D40-4013-83DE-F2FBEC0DDB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C216D3C6-2196-4104-8A4D-906BD2D1CA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t>project_name</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>אתר צי רכב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•תיקים + תיקוני באגים  </t>
   </si>
 </sst>
 </file>
@@ -214,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,9 +235,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -246,12 +246,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -586,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F168A4D5-C056-4D58-82BC-C76224B08C59}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" customWidth="1"/>
@@ -613,7 +607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -667,7 +661,7 @@
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -686,37 +680,37 @@
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>46143</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>46173</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -724,94 +718,112 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>46135</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <v>46136</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>46173</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>46173</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>46126</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="8">
+        <v>46174</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/work_plans.xlsx
+++ b/work_plans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C216D3C6-2196-4104-8A4D-906BD2D1CA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0A9358-4F51-4356-984C-7E540B2855B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
   <si>
     <t>project_name</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t xml:space="preserve">•תיקים + תיקוני באגים  </t>
+  </si>
+  <si>
+    <t>•OTP כניסה אוטומטית
+•עדכון פרטים - תיקון באג שמירת כתובת 
+•תיקון באג - העברה ב"מ
+•הוספת פופ אפ בכניסה לאתר</t>
   </si>
 </sst>
 </file>
@@ -217,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -246,6 +252,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F168A4D5-C056-4D58-82BC-C76224B08C59}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" customWidth="1"/>
@@ -717,18 +726,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>23</v>
+      <c r="C8" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D8" s="11">
-        <v>46135</v>
+        <v>46105</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>6</v>
@@ -740,46 +749,46 @@
         <v>20</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="11">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D10" s="11">
-        <v>46173</v>
+        <v>46136</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="11">
         <v>46173</v>
@@ -791,39 +800,57 @@
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12" s="11">
-        <v>46126</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="6"/>
+        <v>46173</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="11">
+        <v>46126</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D14" s="8">
         <v>46174</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F14" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/work_plans.xlsx
+++ b/work_plans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0A9358-4F51-4356-984C-7E540B2855B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A70D1A2-4155-4ADC-A8BF-79D4F00F5BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>project_name</t>
   </si>
@@ -151,6 +151,12 @@
 •עדכון פרטים - תיקון באג שמירת כתובת 
 •תיקון באג - העברה ב"מ
 •הוספת פופ אפ בכניסה לאתר</t>
+  </si>
+  <si>
+    <t>תיקון באג בהורדת הדוח השנתי מקוצר דרך קיצור דרך בחיפוש עמיתים (גרסת פרונט)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בעקבות שינוי שם של הדוח מהצד של אלטשולר </t>
   </si>
 </sst>
 </file>
@@ -161,7 +167,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -170,7 +176,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -589,14 +595,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F168A4D5-C056-4D58-82BC-C76224B08C59}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.1640625" customWidth="1"/>
-    <col min="3" max="3" width="20.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="20.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -634,7 +640,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -652,7 +658,7 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -670,7 +676,7 @@
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -688,7 +694,7 @@
       </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
@@ -706,7 +712,7 @@
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
@@ -726,7 +732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>20</v>
       </c>
@@ -744,7 +750,7 @@
       </c>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +768,7 @@
       </c>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
@@ -780,7 +786,7 @@
       </c>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
@@ -798,7 +804,7 @@
       </c>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -816,7 +822,7 @@
       </c>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
@@ -834,7 +840,7 @@
       </c>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>5</v>
       </c>
@@ -851,6 +857,26 @@
         <v>16</v>
       </c>
       <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="8">
+        <v>46148</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/work_plans.xlsx
+++ b/work_plans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sivane\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A70D1A2-4155-4ADC-A8BF-79D4F00F5BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223B243A-EE35-43D0-B6F9-FE57982C4FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="35">
   <si>
     <t>project_name</t>
   </si>
@@ -138,9 +138,6 @@
     <t xml:space="preserve">דלק </t>
   </si>
   <si>
-    <t xml:space="preserve">גרסת תיקונים </t>
-  </si>
-  <si>
     <t>אתר צי רכב</t>
   </si>
   <si>
@@ -157,17 +154,25 @@
   </si>
   <si>
     <t xml:space="preserve">בעקבות שינוי שם של הדוח מהצד של אלטשולר </t>
+  </si>
+  <si>
+    <t>העלאת גרסה</t>
+  </si>
+  <si>
+    <t>גרסת תיקונים - 
+•תיקון לתנועות תדלוק מובייל
+• תיקון לתקלת ייצור בחשבוניות</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -176,7 +181,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -190,6 +195,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -229,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -259,6 +270,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -595,14 +609,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F168A4D5-C056-4D58-82BC-C76224B08C59}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.125" customWidth="1"/>
-    <col min="3" max="3" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08203125" customWidth="1"/>
+    <col min="3" max="3" width="20.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -640,7 +654,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -658,7 +672,7 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="93" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -676,7 +690,7 @@
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -694,7 +708,7 @@
       </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
@@ -712,7 +726,7 @@
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
@@ -732,7 +746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>20</v>
       </c>
@@ -740,7 +754,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="11">
         <v>46105</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>20</v>
       </c>
@@ -768,7 +782,7 @@
       </c>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
@@ -786,7 +800,7 @@
       </c>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
@@ -804,7 +818,7 @@
       </c>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -822,60 +836,78 @@
       </c>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="C13" s="13" t="s">
+        <v>34</v>
+      </c>
       <c r="D13" s="11">
-        <v>46126</v>
+        <v>46112</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="8">
-        <v>46174</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="D14" s="11">
+        <v>46126</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="8">
+        <v>46174</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="8">
+        <v>46148</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="D15" s="8">
-        <v>46148</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/work_plans.xlsx
+++ b/work_plans.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223B243A-EE35-43D0-B6F9-FE57982C4FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131E1D0C-3EB6-4250-AB4F-1DC40325C879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{ED5CB1D5-D49C-4E97-93B5-E20B04A5B94F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,9 +135,6 @@
     <t>החלפת המערכת הישנה</t>
   </si>
   <si>
-    <t xml:space="preserve">דלק </t>
-  </si>
-  <si>
     <t>אתר צי רכב</t>
   </si>
   <si>
@@ -162,6 +159,9 @@
     <t>גרסת תיקונים - 
 •תיקון לתנועות תדלוק מובייל
 • תיקון לתקלת ייצור בחשבוניות</t>
+  </si>
+  <si>
+    <t>דלק</t>
   </si>
 </sst>
 </file>
@@ -754,7 +754,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="11">
         <v>46105</v>
@@ -838,13 +838,13 @@
     </row>
     <row r="13" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="C13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="11">
         <v>46112</v>
@@ -856,13 +856,13 @@
     </row>
     <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="11">
         <v>46126</v>
@@ -880,7 +880,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="8">
         <v>46174</v>
@@ -898,7 +898,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="8">
         <v>46148</v>
@@ -907,7 +907,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
